--- a/docs/progress/Testplanung_vorlage.xlsx
+++ b/docs/progress/Testplanung_vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/Dokumentaion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/docs/progress/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410698A8-6BB5-1F4A-903F-92D65E2E4AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46B1641-C7A2-974C-ABE2-BCE0B0888F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="17200" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -106,42 +106,42 @@
     <t>Kein neues Projekt darf hinzugefügt werden</t>
   </si>
   <si>
+    <t>Ein Benuter erstellt eine Information</t>
+  </si>
+  <si>
+    <t>Ein Benutzer kommentiert die Information</t>
+  </si>
+  <si>
+    <t>Suche nach einem Tag innerhalb eines Projekts funktioniert
+Nur die Informationen mit dem gesuchten Tag werden zurückgegeben</t>
+  </si>
+  <si>
+    <t>Kritische Abweichung --&gt; Abnahme gescheitert</t>
+  </si>
+  <si>
+    <t>Hauptfehler, --&gt; Bereinigt bis Datum</t>
+  </si>
+  <si>
+    <t>Nebenfehler --&gt; werden manchmal behoben</t>
+  </si>
+  <si>
     <t>eine Information wird erstellt 
 Information wird dem Projekt hinzugefügt
-Tags sind korrekt gesetzt</t>
-  </si>
-  <si>
-    <t>Ein Benuter erstellt eine Information</t>
-  </si>
-  <si>
-    <t>Ein Benutzer kommentiert die Information</t>
-  </si>
-  <si>
-    <t>Genau 1 neuer Kommentar wurde hinzugefügt 
+Inhalt der Information ist korrekt</t>
+  </si>
+  <si>
+    <t>ein viertes Tag wird hinzugefügt</t>
+  </si>
+  <si>
+    <t>Methode wirft eine Exception</t>
+  </si>
+  <si>
+    <t>Ein Benutzer sucht nach Informationen mit Tag</t>
+  </si>
+  <si>
+    <t>Ein neuer Kommentar wurde hinzugefügt 
 Der Text stimmt
 Der Autor ist korrekt gesetzt, Kommentar ist in der Liste der Kommentare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ein Benutzer sucht nach Informationen mit </t>
-  </si>
-  <si>
-    <t>Suche nach einem Tag innerhalb eines Projekts funktioniert
-Nur die Informationen mit dem gesuchten Tag werden zurückgegeben</t>
-  </si>
-  <si>
-    <t>4 Tags werden erstellt</t>
-  </si>
-  <si>
-    <t>Methode wirft eine Exception, die Information nicht dem Projekt hinzugefügt</t>
-  </si>
-  <si>
-    <t>Kritische Abweichung --&gt; Abnahme gescheitert</t>
-  </si>
-  <si>
-    <t>Hauptfehler, --&gt; Bereinigt bis Datum</t>
-  </si>
-  <si>
-    <t>Nebenfehler --&gt; werden manchmal behoben</t>
   </si>
 </sst>
 </file>
@@ -304,8 +304,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -321,20 +335,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -685,14 +685,14 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -712,7 +712,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -727,7 +727,7 @@
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -742,44 +742,44 @@
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
@@ -787,14 +787,14 @@
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>17</v>
@@ -802,52 +802,52 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>29</v>
+      <c r="E10" s="19" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D11" s="18"/>
-      <c r="E11" s="12"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>30</v>
+      <c r="E12" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D13" s="19"/>
-      <c r="E13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="22"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>31</v>
+      <c r="E14" s="23" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="11"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E16" s="20"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E17" s="20"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E18" s="10"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E19" s="10"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C20" s="7"/>
@@ -869,16 +869,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -886,15 +886,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010047E1B4110D667F4BADC525742D5EE2E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d4242f0faca51ba845790f185672872f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b989ebd0-cfbd-4347-a61d-09d2ec87900e" xmlns:ns3="26aae414-ca61-41d7-9f0a-f5a0a53751b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d27d03a123c6c0eefdfdcad7d866e60f" ns2:_="" ns3:_="">
     <xsd:import namespace="b989ebd0-cfbd-4347-a61d-09d2ec87900e"/>
@@ -1089,6 +1080,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1101,14 +1101,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00B6F33-1652-4D35-BCCC-71D64DD37397}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1127,6 +1119,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD56C91E-EFEF-46AC-A071-D7F993F6AB1F}">
   <ds:schemaRefs>
